--- a/tests/workbooktests/workbooks/test_fxforward.xlsx
+++ b/tests/workbooktests/workbooks/test_fxforward.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC88102-0A13-4F3D-85C1-E8734AA1321B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5FAD45-540B-46F7-BD9C-69BD0E30D807}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{074CAD8B-27E9-4579-8D12-CDBF2E007B7C}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16770" xr2:uid="{074CAD8B-27E9-4579-8D12-CDBF2E007B7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -38,28 +27,6 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
@@ -196,7 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,7 +214,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,13 +547,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E517B80C-7AEE-4C30-AC46-2E03244E5A89}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.625" customWidth="1"/>
+    <col min="2" max="2" width="45.125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -594,16 +561,16 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -614,7 +581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -625,7 +592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -636,7 +603,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -647,19 +614,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="e">
-        <f ca="1">B2+365</f>
-        <v>#VALUE!</v>
+      <c r="B9" s="1">
+        <f>B2+365</f>
+        <v>46539</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -670,7 +637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -681,7 +648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -692,16 +659,16 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlFxForward(B5,B6,B7,B8,B9,B10,B11,B12,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="str">
+        <f t="array" ref="B13">_xll.qlFxForward(B5,B6,B7,B8,B9,B10,B11,B12,B2)</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R13C2FxForward,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -712,7 +679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -723,7 +690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -734,7 +701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -745,19 +712,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="1" t="e">
-        <f ca="1">B2+365</f>
-        <v>#VALUE!</v>
+      <c r="B20" s="1">
+        <f>B2+365</f>
+        <v>46539</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -768,7 +735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -779,7 +746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -790,132 +757,132 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlFxForward2(B16,B17,B18,B19,B20,B21,B22,B23,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="str">
+        <f t="array" ref="B24">_xll.qlFxForward2(B16,B17,B18,B19,B20,B21,B22,B23,B2)</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R24C2FxForward,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B26" ca="1">_xll.qlFxForwardSourceNominal(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
+        <f t="array" ref="B26">_xll.qlFxForwardSourceNominal(B24)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B27" ca="1">_xll.qlFxForwardSourceCurrency(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C27" t="e" cm="1">
-        <f t="array" aca="1" ref="C27" ca="1">_xll.qlCurrencyCode(B27)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="str">
+        <f t="array" ref="B27">_xll.qlFxForwardSourceCurrency(B24)</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R27C2Currency,A</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="array" ref="C27">_xll.qlCurrencyCode(B27)</f>
+        <v>EUR</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B28" ca="1">_xll.qlFxForwardTargetNominal(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <f t="array" ref="B28">_xll.qlFxForwardTargetNominal(B24)</f>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B29" ca="1">_xll.qlFxForwardTargetCurrency(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C29" t="e" cm="1">
-        <f t="array" aca="1" ref="C29" ca="1">_xll.qlCurrencyCode(B29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="str">
+        <f t="array" ref="B29">_xll.qlFxForwardTargetCurrency(B24)</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R29C2Currency,A</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="array" ref="C29">_xll.qlCurrencyCode(B29)</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B30" ca="1">_xll.qlFxForwardMaturityDate(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="1">
+        <f t="array" ref="B30">_xll.qlFxForwardMaturityDate(B24)</f>
+        <v>46539</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B31" ca="1">_xll.qlFxForwardPaySourceCurrency(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="b">
+        <f t="array" ref="B31">_xll.qlFxForwardPaySourceCurrency(B24)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B32" ca="1">_xll.qlFxForwardForwardRate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
+        <f t="array" ref="B32">_xll.qlFxForwardForwardRate(B13)</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B33" ca="1">_xll.qlFxForwardSettlementDays(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
+        <f t="array" ref="B33">_xll.qlFxForwardSettlementDays(B13)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B34" ca="1">_xll.qlFxForwardSettlementCalendar(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="str">
+        <f t="array" ref="B34">_xll.qlFxForwardSettlementCalendar(B13)</f>
+        <v>Null</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B35" ca="1">_xll.qlFxForwardSettlementDate(B13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="1">
+        <f t="array" ref="B35">_xll.qlFxForwardSettlementDate(B13)</f>
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B38" ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R38C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B39" ca="1">_xll.qlFlatForward(B3,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="str">
+        <f>_xll.qlFlatForward(B3,0.03,"actual365fixed")</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R39C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -923,49 +890,49 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="15">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B41" ca="1">_xll.qlDiscountingFxForwardEngine(B38,B39,B40,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="str">
+        <f t="array" ref="B41">_xll.qlDiscountingFxForwardEngine(B38,B39,B40,B2)</f>
+        <v>欣[test_fxforward.xlsx]Sheet1!R41C2DiscountingFxForwardEngine,A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B43" ca="1">_xll.qlInstrumentNPV(B13,_xll.qlInstrumentSetPricingEngine(B13,B41))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="4">
+        <f t="array" ref="B43">_xll.qlInstrumentNPV(B13,_xll.qlInstrumentSetPricingEngine(B13,B41))</f>
+        <v>-388.24202878162941</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B44" ca="1">_xll.qlFxForwardFairForwardRate(B13,B43)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="3">
+        <f t="array" ref="B44">_xll.qlFxForwardFairForwardRate(B13,B43)</f>
+        <v>1.2500000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B45" ca="1">_xll.qlFxForwardNpvSourceCurrency(B13,B43)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="4">
+        <f t="array" ref="B45">_xll.qlFxForwardNpvSourceCurrency(B13,B43)</f>
+        <v>-388.24202878162941</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B46" ca="1">_xll.qlFxForwardNpvTargetCurrency(B13,B43)</f>
-        <v>#VALUE!</v>
+      <c r="B46" s="4">
+        <f t="array" ref="B46">_xll.qlFxForwardNpvTargetCurrency(B13,B43)</f>
+        <v>-485.30253597703677</v>
       </c>
     </row>
   </sheetData>
